--- a/public/names.xlsx
+++ b/public/names.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="557">
   <si>
     <t>适用兵种</t>
   </si>
@@ -574,6 +574,297 @@
     <t>蒋钦</t>
   </si>
   <si>
+    <t>董昭</t>
+  </si>
+  <si>
+    <t>王朗</t>
+  </si>
+  <si>
+    <t>华歆</t>
+  </si>
+  <si>
+    <t>郑玄</t>
+  </si>
+  <si>
+    <t>管辂</t>
+  </si>
+  <si>
+    <t>伊籍</t>
+  </si>
+  <si>
+    <t>孙乾</t>
+  </si>
+  <si>
+    <t>简雍</t>
+  </si>
+  <si>
+    <t>糜竺</t>
+  </si>
+  <si>
+    <t>糜芳</t>
+  </si>
+  <si>
+    <t>陈震</t>
+  </si>
+  <si>
+    <t>宗预</t>
+  </si>
+  <si>
+    <t>廖立</t>
+  </si>
+  <si>
+    <t>秦宓</t>
+  </si>
+  <si>
+    <t>张温</t>
+  </si>
+  <si>
+    <t>阚泽</t>
+  </si>
+  <si>
+    <t>虞翻</t>
+  </si>
+  <si>
+    <t>薛综</t>
+  </si>
+  <si>
+    <t>华佗</t>
+  </si>
+  <si>
+    <t>麴义</t>
+  </si>
+  <si>
+    <t>苏由</t>
+  </si>
+  <si>
+    <t>马延</t>
+  </si>
+  <si>
+    <t>张南</t>
+  </si>
+  <si>
+    <t>焦触</t>
+  </si>
+  <si>
+    <t>吕旷</t>
+  </si>
+  <si>
+    <t>吕翔</t>
+  </si>
+  <si>
+    <t>韩猛</t>
+  </si>
+  <si>
+    <t>淳于琼</t>
+  </si>
+  <si>
+    <t>高览</t>
+  </si>
+  <si>
+    <t>蒋义渠</t>
+  </si>
+  <si>
+    <t>吕公</t>
+  </si>
+  <si>
+    <t>蔡瑁</t>
+  </si>
+  <si>
+    <t>张允</t>
+  </si>
+  <si>
+    <t>王威</t>
+  </si>
+  <si>
+    <t>霍峻</t>
+  </si>
+  <si>
+    <t>向宠</t>
+  </si>
+  <si>
+    <t>傅佥</t>
+  </si>
+  <si>
+    <t>蒋舒</t>
+  </si>
+  <si>
+    <t>马忠</t>
+  </si>
+  <si>
+    <t>吕凯</t>
+  </si>
+  <si>
+    <t>王颀</t>
+  </si>
+  <si>
+    <t>牵招</t>
+  </si>
+  <si>
+    <t>田豫</t>
+  </si>
+  <si>
+    <t>李儒</t>
+  </si>
+  <si>
+    <t>樊稠</t>
+  </si>
+  <si>
+    <t>郭汜</t>
+  </si>
+  <si>
+    <t>李傕</t>
+  </si>
+  <si>
+    <t>张济</t>
+  </si>
+  <si>
+    <t>段煨</t>
+  </si>
+  <si>
+    <t>胡轸</t>
+  </si>
+  <si>
+    <t>徐荣</t>
+  </si>
+  <si>
+    <t>牛辅</t>
+  </si>
+  <si>
+    <t>杨奉</t>
+  </si>
+  <si>
+    <t>韩暹</t>
+  </si>
+  <si>
+    <t>波才</t>
+  </si>
+  <si>
+    <t>张曼成</t>
+  </si>
+  <si>
+    <t>赵弘</t>
+  </si>
+  <si>
+    <t>孙夏</t>
+  </si>
+  <si>
+    <t>韩忠</t>
+  </si>
+  <si>
+    <t>严政</t>
+  </si>
+  <si>
+    <t>高升</t>
+  </si>
+  <si>
+    <t>邓茂</t>
+  </si>
+  <si>
+    <t>程远志</t>
+  </si>
+  <si>
+    <t>张梁</t>
+  </si>
+  <si>
+    <t>张宝</t>
+  </si>
+  <si>
+    <t>张角</t>
+  </si>
+  <si>
+    <t>凌操</t>
+  </si>
+  <si>
+    <t>董袭</t>
+  </si>
+  <si>
+    <t>陈就</t>
+  </si>
+  <si>
+    <t>吕介</t>
+  </si>
+  <si>
+    <t>刘贤</t>
+  </si>
+  <si>
+    <t>杨龄</t>
+  </si>
+  <si>
+    <t>金旋</t>
+  </si>
+  <si>
+    <t>赵范</t>
+  </si>
+  <si>
+    <t>鲍隆</t>
+  </si>
+  <si>
+    <t>陈应</t>
+  </si>
+  <si>
+    <t>韩玄</t>
+  </si>
+  <si>
+    <t>费诗</t>
+  </si>
+  <si>
+    <t>彭羕</t>
+  </si>
+  <si>
+    <t>孟达</t>
+  </si>
+  <si>
+    <t>黄权</t>
+  </si>
+  <si>
+    <t>吴兰</t>
+  </si>
+  <si>
+    <t>任夔</t>
+  </si>
+  <si>
+    <t>泠苞</t>
+  </si>
+  <si>
+    <t>邓贤</t>
+  </si>
+  <si>
+    <t>刘璝</t>
+  </si>
+  <si>
+    <t>张任</t>
+  </si>
+  <si>
+    <t>卓膺</t>
+  </si>
+  <si>
+    <t>严颜</t>
+  </si>
+  <si>
+    <t>李恢</t>
+  </si>
+  <si>
+    <t>张嶷</t>
+  </si>
+  <si>
+    <t>柳隐</t>
+  </si>
+  <si>
+    <t>盛曼</t>
+  </si>
+  <si>
+    <t>句扶</t>
+  </si>
+  <si>
+    <t>马谡</t>
+  </si>
+  <si>
+    <t>高翔</t>
+  </si>
+  <si>
+    <t>胡济</t>
+  </si>
+  <si>
     <t>Zhuge Liang</t>
   </si>
   <si>
@@ -1106,6 +1397,294 @@
   </si>
   <si>
     <t>Jiang Qin</t>
+  </si>
+  <si>
+    <t>Dong Zhao</t>
+  </si>
+  <si>
+    <t>Wang Lang</t>
+  </si>
+  <si>
+    <t>Hua Xin</t>
+  </si>
+  <si>
+    <t>Zheng Xuan</t>
+  </si>
+  <si>
+    <t>Guan Lu</t>
+  </si>
+  <si>
+    <t>Yi Ji</t>
+  </si>
+  <si>
+    <t>Sun Qian</t>
+  </si>
+  <si>
+    <t>Jian Yong</t>
+  </si>
+  <si>
+    <t>Mi Zhu</t>
+  </si>
+  <si>
+    <t>Mi Fang</t>
+  </si>
+  <si>
+    <t>Chen Zhen</t>
+  </si>
+  <si>
+    <t>Zong Yu</t>
+  </si>
+  <si>
+    <t>Liao Li</t>
+  </si>
+  <si>
+    <t>Qin Mi</t>
+  </si>
+  <si>
+    <t>Zhang Wen</t>
+  </si>
+  <si>
+    <t>Kan Ze</t>
+  </si>
+  <si>
+    <t>Yu Fan</t>
+  </si>
+  <si>
+    <t>Xue Zong</t>
+  </si>
+  <si>
+    <t>Hua Tuo</t>
+  </si>
+  <si>
+    <t>Qu Yi</t>
+  </si>
+  <si>
+    <t>Su You</t>
+  </si>
+  <si>
+    <t>Ma Yan</t>
+  </si>
+  <si>
+    <t>Zhang Nan</t>
+  </si>
+  <si>
+    <t>Jiao Chu</t>
+  </si>
+  <si>
+    <t>Lu Kuang</t>
+  </si>
+  <si>
+    <t>Lu Xiang</t>
+  </si>
+  <si>
+    <t>Han Meng</t>
+  </si>
+  <si>
+    <t>Chunyu Qiong</t>
+  </si>
+  <si>
+    <t>Gao Lan</t>
+  </si>
+  <si>
+    <t>Jiang Yiqu</t>
+  </si>
+  <si>
+    <t>Lu Gong</t>
+  </si>
+  <si>
+    <t>Cai Mao</t>
+  </si>
+  <si>
+    <t>Zhang Yun</t>
+  </si>
+  <si>
+    <t>Wang Wei</t>
+  </si>
+  <si>
+    <t>Huo Jun</t>
+  </si>
+  <si>
+    <t>Xiang Chong</t>
+  </si>
+  <si>
+    <t>Fu Qian</t>
+  </si>
+  <si>
+    <t>Jiang Shu</t>
+  </si>
+  <si>
+    <t>Ma Zhong</t>
+  </si>
+  <si>
+    <t>Lu Kai</t>
+  </si>
+  <si>
+    <t>Wang Qi</t>
+  </si>
+  <si>
+    <t>Qian Zhao</t>
+  </si>
+  <si>
+    <t>Tian Yu</t>
+  </si>
+  <si>
+    <t>Li Ru</t>
+  </si>
+  <si>
+    <t>Fan Chou</t>
+  </si>
+  <si>
+    <t>Guo Si</t>
+  </si>
+  <si>
+    <t>Li Jue</t>
+  </si>
+  <si>
+    <t>Zhang Ji</t>
+  </si>
+  <si>
+    <t>Duan Wei</t>
+  </si>
+  <si>
+    <t>Hu Zhen</t>
+  </si>
+  <si>
+    <t>Xu Rong</t>
+  </si>
+  <si>
+    <t>Niu Fu</t>
+  </si>
+  <si>
+    <t>Yang Feng</t>
+  </si>
+  <si>
+    <t>Han Xian</t>
+  </si>
+  <si>
+    <t>Bo Cai</t>
+  </si>
+  <si>
+    <t>Zhang Mancheng</t>
+  </si>
+  <si>
+    <t>Zhao Hong</t>
+  </si>
+  <si>
+    <t>Sun Xia</t>
+  </si>
+  <si>
+    <t>Han Zhong</t>
+  </si>
+  <si>
+    <t>Yan Zheng</t>
+  </si>
+  <si>
+    <t>Gao Sheng</t>
+  </si>
+  <si>
+    <t>Deng Mao</t>
+  </si>
+  <si>
+    <t>Cheng Yuanzhi</t>
+  </si>
+  <si>
+    <t>Zhang Liang</t>
+  </si>
+  <si>
+    <t>Zhang Jiao</t>
+  </si>
+  <si>
+    <t>Ling Cao</t>
+  </si>
+  <si>
+    <t>Dong Xi</t>
+  </si>
+  <si>
+    <t>Chen Jiu</t>
+  </si>
+  <si>
+    <t>Lu Jie</t>
+  </si>
+  <si>
+    <t>Liu Xian</t>
+  </si>
+  <si>
+    <t>Yang Ling</t>
+  </si>
+  <si>
+    <t>Jin Xuan</t>
+  </si>
+  <si>
+    <t>Zhao Fan</t>
+  </si>
+  <si>
+    <t>Bao Long</t>
+  </si>
+  <si>
+    <t>Chen Ying</t>
+  </si>
+  <si>
+    <t>Han Xuan</t>
+  </si>
+  <si>
+    <t>Fei Shi</t>
+  </si>
+  <si>
+    <t>Peng Yang</t>
+  </si>
+  <si>
+    <t>Meng Da</t>
+  </si>
+  <si>
+    <t>Huang Quan</t>
+  </si>
+  <si>
+    <t>Wu Lan</t>
+  </si>
+  <si>
+    <t>Ren Kui</t>
+  </si>
+  <si>
+    <t>Ling Bao</t>
+  </si>
+  <si>
+    <t>Deng Xian</t>
+  </si>
+  <si>
+    <t>Liu Gui</t>
+  </si>
+  <si>
+    <t>Zhang Ren</t>
+  </si>
+  <si>
+    <t>Zhuo Ying</t>
+  </si>
+  <si>
+    <t>Yan Yan</t>
+  </si>
+  <si>
+    <t>Li Hui</t>
+  </si>
+  <si>
+    <t>Zhang Ni</t>
+  </si>
+  <si>
+    <t>Liu Yin</t>
+  </si>
+  <si>
+    <t>Sheng Man</t>
+  </si>
+  <si>
+    <t>Ju Fu</t>
+  </si>
+  <si>
+    <t>Ma Su</t>
+  </si>
+  <si>
+    <t>Gao Xiang</t>
+  </si>
+  <si>
+    <t>Hu Ji</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1488,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>283</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -1502,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -1516,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -1530,7 +2109,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1544,7 +2123,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1558,7 +2137,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1572,7 +2151,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1586,7 +2165,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1600,7 +2179,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>291</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1614,7 +2193,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1628,7 +2207,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1642,7 +2221,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -1656,7 +2235,7 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -1670,7 +2249,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1684,7 +2263,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1698,7 +2277,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1712,7 +2291,7 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1726,7 +2305,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1740,7 +2319,7 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1754,7 +2333,7 @@
         <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1768,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1782,7 +2361,7 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -1796,7 +2375,7 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1810,7 +2389,7 @@
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1824,7 +2403,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>307</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -1838,7 +2417,7 @@
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1852,7 +2431,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -1866,7 +2445,7 @@
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -1880,7 +2459,7 @@
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>214</v>
+        <v>311</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -1894,7 +2473,7 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>312</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -1908,7 +2487,7 @@
         <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -1922,7 +2501,7 @@
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>217</v>
+        <v>314</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1936,7 +2515,7 @@
         <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>315</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -1950,7 +2529,7 @@
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -1964,7 +2543,7 @@
         <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -1978,7 +2557,7 @@
         <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>318</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -1992,7 +2571,7 @@
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>319</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -2006,7 +2585,7 @@
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>320</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -2020,7 +2599,7 @@
         <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>321</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2034,7 +2613,7 @@
         <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2048,7 +2627,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2062,7 +2641,7 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>324</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -2076,7 +2655,7 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -2090,7 +2669,7 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2104,7 +2683,7 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>327</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2118,7 +2697,7 @@
         <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -2132,7 +2711,7 @@
         <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>329</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -2146,7 +2725,7 @@
         <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>330</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -2160,7 +2739,7 @@
         <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="D50">
         <v>6</v>
@@ -2174,7 +2753,7 @@
         <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>235</v>
+        <v>332</v>
       </c>
       <c r="D51">
         <v>6</v>
@@ -2188,7 +2767,7 @@
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="D52">
         <v>6</v>
@@ -2202,7 +2781,7 @@
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>334</v>
       </c>
       <c r="D53">
         <v>6</v>
@@ -2216,7 +2795,7 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>238</v>
+        <v>335</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -2230,7 +2809,7 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>239</v>
+        <v>336</v>
       </c>
       <c r="D55">
         <v>5</v>
@@ -2244,7 +2823,7 @@
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>337</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -2258,7 +2837,7 @@
         <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -2272,7 +2851,7 @@
         <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>242</v>
+        <v>339</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2286,7 +2865,7 @@
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="D59">
         <v>5</v>
@@ -2300,7 +2879,7 @@
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -2314,7 +2893,7 @@
         <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>245</v>
+        <v>342</v>
       </c>
       <c r="D61">
         <v>5</v>
@@ -2328,7 +2907,7 @@
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="D62">
         <v>5</v>
@@ -2342,7 +2921,7 @@
         <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>344</v>
       </c>
       <c r="D63">
         <v>5</v>
@@ -2356,7 +2935,7 @@
         <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>248</v>
+        <v>345</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2370,7 +2949,7 @@
         <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="D65">
         <v>4</v>
@@ -2384,7 +2963,7 @@
         <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>250</v>
+        <v>347</v>
       </c>
       <c r="D66">
         <v>4</v>
@@ -2398,7 +2977,7 @@
         <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>348</v>
       </c>
       <c r="D67">
         <v>5</v>
@@ -2412,7 +2991,7 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>252</v>
+        <v>349</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -2426,7 +3005,7 @@
         <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>350</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -2440,7 +3019,7 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>254</v>
+        <v>351</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -2454,7 +3033,7 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>352</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -2468,7 +3047,7 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -2482,7 +3061,7 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>257</v>
+        <v>354</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -2496,7 +3075,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>258</v>
+        <v>355</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -2510,7 +3089,7 @@
         <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>356</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -2524,7 +3103,7 @@
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -2538,7 +3117,7 @@
         <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>358</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -2552,7 +3131,7 @@
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>262</v>
+        <v>359</v>
       </c>
       <c r="D78">
         <v>4</v>
@@ -2566,7 +3145,7 @@
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>263</v>
+        <v>360</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -2580,7 +3159,7 @@
         <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>264</v>
+        <v>361</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -2594,7 +3173,7 @@
         <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>362</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -2608,7 +3187,7 @@
         <v>88</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>363</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -2622,7 +3201,7 @@
         <v>89</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>364</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -2636,7 +3215,7 @@
         <v>90</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>365</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -2650,7 +3229,7 @@
         <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>269</v>
+        <v>366</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -2664,7 +3243,7 @@
         <v>92</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>367</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -2678,7 +3257,7 @@
         <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>271</v>
+        <v>368</v>
       </c>
       <c r="D87">
         <v>4</v>
@@ -2692,7 +3271,7 @@
         <v>94</v>
       </c>
       <c r="C88" t="s">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -2706,7 +3285,7 @@
         <v>95</v>
       </c>
       <c r="C89" t="s">
-        <v>273</v>
+        <v>370</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -2720,7 +3299,7 @@
         <v>96</v>
       </c>
       <c r="C90" t="s">
-        <v>274</v>
+        <v>371</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -2734,7 +3313,7 @@
         <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -2748,7 +3327,7 @@
         <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>276</v>
+        <v>373</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2762,7 +3341,7 @@
         <v>99</v>
       </c>
       <c r="C93" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -2776,7 +3355,7 @@
         <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2790,7 +3369,7 @@
         <v>101</v>
       </c>
       <c r="C95" t="s">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -2804,7 +3383,7 @@
         <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>280</v>
+        <v>377</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -2818,7 +3397,7 @@
         <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -2832,7 +3411,7 @@
         <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>379</v>
       </c>
       <c r="D98">
         <v>6</v>
@@ -2846,7 +3425,7 @@
         <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>283</v>
+        <v>380</v>
       </c>
       <c r="D99">
         <v>6</v>
@@ -2860,7 +3439,7 @@
         <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>284</v>
+        <v>381</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -2874,7 +3453,7 @@
         <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
       <c r="D101">
         <v>6</v>
@@ -2888,7 +3467,7 @@
         <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>286</v>
+        <v>383</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2902,7 +3481,7 @@
         <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="D103">
         <v>5</v>
@@ -2916,7 +3495,7 @@
         <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="D104">
         <v>6</v>
@@ -2930,7 +3509,7 @@
         <v>111</v>
       </c>
       <c r="C105" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -2944,7 +3523,7 @@
         <v>112</v>
       </c>
       <c r="C106" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="D106">
         <v>4</v>
@@ -2958,7 +3537,7 @@
         <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -2972,7 +3551,7 @@
         <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -2986,7 +3565,7 @@
         <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>293</v>
+        <v>390</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -3000,7 +3579,7 @@
         <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>294</v>
+        <v>391</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -3014,7 +3593,7 @@
         <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>295</v>
+        <v>392</v>
       </c>
       <c r="D111">
         <v>3</v>
@@ -3028,7 +3607,7 @@
         <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>296</v>
+        <v>393</v>
       </c>
       <c r="D112">
         <v>4</v>
@@ -3042,7 +3621,7 @@
         <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>297</v>
+        <v>394</v>
       </c>
       <c r="D113">
         <v>4</v>
@@ -3056,7 +3635,7 @@
         <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>298</v>
+        <v>395</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -3070,7 +3649,7 @@
         <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>299</v>
+        <v>396</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -3084,7 +3663,7 @@
         <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -3098,7 +3677,7 @@
         <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="D117">
         <v>3</v>
@@ -3112,7 +3691,7 @@
         <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -3126,7 +3705,7 @@
         <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>303</v>
+        <v>400</v>
       </c>
       <c r="D119">
         <v>3</v>
@@ -3140,7 +3719,7 @@
         <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -3154,7 +3733,7 @@
         <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>305</v>
+        <v>402</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -3168,7 +3747,7 @@
         <v>128</v>
       </c>
       <c r="C122" t="s">
-        <v>306</v>
+        <v>403</v>
       </c>
       <c r="D122">
         <v>4</v>
@@ -3182,7 +3761,7 @@
         <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -3196,7 +3775,7 @@
         <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -3210,7 +3789,7 @@
         <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="D125">
         <v>5</v>
@@ -3224,7 +3803,7 @@
         <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>310</v>
+        <v>407</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -3238,7 +3817,7 @@
         <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>311</v>
+        <v>408</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -3252,7 +3831,7 @@
         <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="D128">
         <v>2</v>
@@ -3266,7 +3845,7 @@
         <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>313</v>
+        <v>410</v>
       </c>
       <c r="D129">
         <v>3</v>
@@ -3280,7 +3859,7 @@
         <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -3294,7 +3873,7 @@
         <v>137</v>
       </c>
       <c r="C131" t="s">
-        <v>315</v>
+        <v>412</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -3308,7 +3887,7 @@
         <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>316</v>
+        <v>413</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -3322,7 +3901,7 @@
         <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>317</v>
+        <v>414</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -3336,7 +3915,7 @@
         <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -3350,7 +3929,7 @@
         <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>319</v>
+        <v>416</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -3364,7 +3943,7 @@
         <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>320</v>
+        <v>417</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -3378,7 +3957,7 @@
         <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>321</v>
+        <v>418</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -3392,7 +3971,7 @@
         <v>144</v>
       </c>
       <c r="C138" t="s">
-        <v>322</v>
+        <v>419</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -3406,7 +3985,7 @@
         <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -3420,7 +3999,7 @@
         <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -3434,7 +4013,7 @@
         <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -3448,7 +4027,7 @@
         <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -3462,7 +4041,7 @@
         <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>327</v>
+        <v>424</v>
       </c>
       <c r="D143">
         <v>6</v>
@@ -3473,13 +4052,13 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3487,13 +4066,13 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>285</v>
+        <v>426</v>
       </c>
       <c r="D145">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3501,13 +4080,13 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>234</v>
+        <v>427</v>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3515,10 +4094,10 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>200</v>
+        <v>428</v>
       </c>
       <c r="D147">
         <v>5</v>
@@ -3529,10 +4108,10 @@
         <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="D148">
         <v>4</v>
@@ -3543,13 +4122,13 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>329</v>
+        <v>430</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3557,13 +4136,13 @@
         <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>330</v>
+        <v>431</v>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3571,13 +4150,13 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>331</v>
+        <v>432</v>
       </c>
       <c r="D151">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3585,13 +4164,13 @@
         <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
-        <v>332</v>
+        <v>433</v>
       </c>
       <c r="D152">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3599,10 +4178,10 @@
         <v>7</v>
       </c>
       <c r="B153" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C153" t="s">
-        <v>333</v>
+        <v>434</v>
       </c>
       <c r="D153">
         <v>4</v>
@@ -3613,13 +4192,13 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C154" t="s">
-        <v>334</v>
+        <v>435</v>
       </c>
       <c r="D154">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3627,13 +4206,13 @@
         <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C155" t="s">
-        <v>335</v>
+        <v>436</v>
       </c>
       <c r="D155">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3641,13 +4220,13 @@
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C156" t="s">
-        <v>336</v>
+        <v>437</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3655,13 +4234,13 @@
         <v>7</v>
       </c>
       <c r="B157" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C157" t="s">
-        <v>337</v>
+        <v>438</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3669,10 +4248,10 @@
         <v>7</v>
       </c>
       <c r="B158" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C158" t="s">
-        <v>338</v>
+        <v>439</v>
       </c>
       <c r="D158">
         <v>3</v>
@@ -3683,13 +4262,13 @@
         <v>7</v>
       </c>
       <c r="B159" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="C159" t="s">
-        <v>255</v>
+        <v>440</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3697,10 +4276,10 @@
         <v>7</v>
       </c>
       <c r="B160" t="s">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="C160" t="s">
-        <v>256</v>
+        <v>441</v>
       </c>
       <c r="D160">
         <v>3</v>
@@ -3711,10 +4290,10 @@
         <v>7</v>
       </c>
       <c r="B161" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="C161" t="s">
-        <v>252</v>
+        <v>442</v>
       </c>
       <c r="D161">
         <v>3</v>
@@ -3725,13 +4304,13 @@
         <v>7</v>
       </c>
       <c r="B162" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="C162" t="s">
-        <v>253</v>
+        <v>443</v>
       </c>
       <c r="D162">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3739,13 +4318,13 @@
         <v>7</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C163" t="s">
-        <v>339</v>
+        <v>444</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3753,13 +4332,13 @@
         <v>7</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="C164" t="s">
-        <v>190</v>
+        <v>445</v>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3767,13 +4346,13 @@
         <v>7</v>
       </c>
       <c r="B165" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="C165" t="s">
-        <v>191</v>
+        <v>446</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3781,13 +4360,13 @@
         <v>7</v>
       </c>
       <c r="B166" t="s">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s">
-        <v>263</v>
+        <v>447</v>
       </c>
       <c r="D166">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3795,13 +4374,13 @@
         <v>7</v>
       </c>
       <c r="B167" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C167" t="s">
-        <v>340</v>
+        <v>448</v>
       </c>
       <c r="D167">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3809,10 +4388,10 @@
         <v>7</v>
       </c>
       <c r="B168" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C168" t="s">
-        <v>341</v>
+        <v>449</v>
       </c>
       <c r="D168">
         <v>3</v>
@@ -3823,13 +4402,13 @@
         <v>7</v>
       </c>
       <c r="B169" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C169" t="s">
-        <v>342</v>
+        <v>450</v>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3837,13 +4416,13 @@
         <v>7</v>
       </c>
       <c r="B170" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C170" t="s">
-        <v>343</v>
+        <v>451</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3851,13 +4430,13 @@
         <v>7</v>
       </c>
       <c r="B171" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C171" t="s">
-        <v>344</v>
+        <v>452</v>
       </c>
       <c r="D171">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3865,10 +4444,10 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C172" t="s">
-        <v>345</v>
+        <v>453</v>
       </c>
       <c r="D172">
         <v>3</v>
@@ -3879,13 +4458,13 @@
         <v>7</v>
       </c>
       <c r="B173" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C173" t="s">
-        <v>346</v>
+        <v>454</v>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3893,13 +4472,13 @@
         <v>7</v>
       </c>
       <c r="B174" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C174" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3907,10 +4486,10 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>456</v>
       </c>
       <c r="D175">
         <v>2</v>
@@ -3921,13 +4500,13 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C176" t="s">
-        <v>349</v>
+        <v>457</v>
       </c>
       <c r="D176">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3935,10 +4514,10 @@
         <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C177" t="s">
-        <v>350</v>
+        <v>458</v>
       </c>
       <c r="D177">
         <v>2</v>
@@ -3949,13 +4528,13 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C178" t="s">
-        <v>351</v>
+        <v>459</v>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3963,10 +4542,10 @@
         <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C179" t="s">
-        <v>352</v>
+        <v>460</v>
       </c>
       <c r="D179">
         <v>3</v>
@@ -3974,27 +4553,27 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B180" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C180" t="s">
-        <v>353</v>
+        <v>461</v>
       </c>
       <c r="D180">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B181" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C181" t="s">
-        <v>354</v>
+        <v>462</v>
       </c>
       <c r="D181">
         <v>3</v>
@@ -4002,41 +4581,41 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B182" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C182" t="s">
-        <v>355</v>
+        <v>463</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B183" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="C183" t="s">
-        <v>356</v>
+        <v>464</v>
       </c>
       <c r="D183">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B184" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C184" t="s">
-        <v>357</v>
+        <v>465</v>
       </c>
       <c r="D184">
         <v>3</v>
@@ -4044,27 +4623,27 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B185" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C185" t="s">
-        <v>358</v>
+        <v>466</v>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B186" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C186" t="s">
-        <v>359</v>
+        <v>467</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -4072,27 +4651,27 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B187" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C187" t="s">
-        <v>360</v>
+        <v>468</v>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B188" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C188" t="s">
-        <v>361</v>
+        <v>469</v>
       </c>
       <c r="D188">
         <v>2</v>
@@ -4100,30 +4679,1234 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B189" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C189" t="s">
-        <v>362</v>
+        <v>470</v>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B190" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C190" t="s">
-        <v>363</v>
+        <v>471</v>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>4</v>
+      </c>
+      <c r="B191" t="s">
+        <v>197</v>
+      </c>
+      <c r="C191" t="s">
+        <v>472</v>
+      </c>
+      <c r="D191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>4</v>
+      </c>
+      <c r="B192" t="s">
+        <v>198</v>
+      </c>
+      <c r="C192" t="s">
+        <v>473</v>
+      </c>
+      <c r="D192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>4</v>
+      </c>
+      <c r="B193" t="s">
+        <v>199</v>
+      </c>
+      <c r="C193" t="s">
+        <v>474</v>
+      </c>
+      <c r="D193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>4</v>
+      </c>
+      <c r="B194" t="s">
+        <v>200</v>
+      </c>
+      <c r="C194" t="s">
+        <v>475</v>
+      </c>
+      <c r="D194">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>4</v>
+      </c>
+      <c r="B195" t="s">
+        <v>201</v>
+      </c>
+      <c r="C195" t="s">
+        <v>476</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>4</v>
+      </c>
+      <c r="B196" t="s">
+        <v>202</v>
+      </c>
+      <c r="C196" t="s">
+        <v>477</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" t="s">
+        <v>203</v>
+      </c>
+      <c r="C197" t="s">
+        <v>478</v>
+      </c>
+      <c r="D197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>4</v>
+      </c>
+      <c r="B198" t="s">
+        <v>204</v>
+      </c>
+      <c r="C198" t="s">
+        <v>479</v>
+      </c>
+      <c r="D198">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>5</v>
+      </c>
+      <c r="B199" t="s">
+        <v>205</v>
+      </c>
+      <c r="C199" t="s">
+        <v>480</v>
+      </c>
+      <c r="D199">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>5</v>
+      </c>
+      <c r="B200" t="s">
+        <v>206</v>
+      </c>
+      <c r="C200" t="s">
+        <v>481</v>
+      </c>
+      <c r="D200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>5</v>
+      </c>
+      <c r="B201" t="s">
+        <v>207</v>
+      </c>
+      <c r="C201" t="s">
+        <v>482</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B202" t="s">
+        <v>208</v>
+      </c>
+      <c r="C202" t="s">
+        <v>483</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>5</v>
+      </c>
+      <c r="B203" t="s">
+        <v>209</v>
+      </c>
+      <c r="C203" t="s">
+        <v>484</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>5</v>
+      </c>
+      <c r="B204" t="s">
+        <v>210</v>
+      </c>
+      <c r="C204" t="s">
+        <v>485</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>5</v>
+      </c>
+      <c r="B205" t="s">
+        <v>211</v>
+      </c>
+      <c r="C205" t="s">
+        <v>486</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>5</v>
+      </c>
+      <c r="B206" t="s">
+        <v>212</v>
+      </c>
+      <c r="C206" t="s">
+        <v>487</v>
+      </c>
+      <c r="D206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
+        <v>5</v>
+      </c>
+      <c r="B207" t="s">
+        <v>213</v>
+      </c>
+      <c r="C207" t="s">
+        <v>488</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
+        <v>5</v>
+      </c>
+      <c r="B208" t="s">
+        <v>214</v>
+      </c>
+      <c r="C208" t="s">
+        <v>489</v>
+      </c>
+      <c r="D208">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
+        <v>5</v>
+      </c>
+      <c r="B209" t="s">
+        <v>215</v>
+      </c>
+      <c r="C209" t="s">
+        <v>490</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" t="s">
+        <v>216</v>
+      </c>
+      <c r="C210" t="s">
+        <v>491</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
+        <v>5</v>
+      </c>
+      <c r="B211" t="s">
+        <v>217</v>
+      </c>
+      <c r="C211" t="s">
+        <v>492</v>
+      </c>
+      <c r="D211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
+        <v>5</v>
+      </c>
+      <c r="B212" t="s">
+        <v>218</v>
+      </c>
+      <c r="C212" t="s">
+        <v>493</v>
+      </c>
+      <c r="D212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
+        <v>5</v>
+      </c>
+      <c r="B213" t="s">
+        <v>219</v>
+      </c>
+      <c r="C213" t="s">
+        <v>494</v>
+      </c>
+      <c r="D213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
+        <v>5</v>
+      </c>
+      <c r="B214" t="s">
+        <v>220</v>
+      </c>
+      <c r="C214" t="s">
+        <v>495</v>
+      </c>
+      <c r="D214">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" t="s">
+        <v>221</v>
+      </c>
+      <c r="C215" t="s">
+        <v>496</v>
+      </c>
+      <c r="D215">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
+        <v>5</v>
+      </c>
+      <c r="B216" t="s">
+        <v>222</v>
+      </c>
+      <c r="C216" t="s">
+        <v>497</v>
+      </c>
+      <c r="D216">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
+        <v>5</v>
+      </c>
+      <c r="B217" t="s">
+        <v>223</v>
+      </c>
+      <c r="C217" t="s">
+        <v>498</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
+        <v>5</v>
+      </c>
+      <c r="B218" t="s">
+        <v>224</v>
+      </c>
+      <c r="C218" t="s">
+        <v>499</v>
+      </c>
+      <c r="D218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
+        <v>5</v>
+      </c>
+      <c r="B219" t="s">
+        <v>225</v>
+      </c>
+      <c r="C219" t="s">
+        <v>500</v>
+      </c>
+      <c r="D219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
+        <v>5</v>
+      </c>
+      <c r="B220" t="s">
+        <v>226</v>
+      </c>
+      <c r="C220" t="s">
+        <v>501</v>
+      </c>
+      <c r="D220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>5</v>
+      </c>
+      <c r="B221" t="s">
+        <v>227</v>
+      </c>
+      <c r="C221" t="s">
+        <v>502</v>
+      </c>
+      <c r="D221">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>5</v>
+      </c>
+      <c r="B222" t="s">
+        <v>228</v>
+      </c>
+      <c r="C222" t="s">
+        <v>503</v>
+      </c>
+      <c r="D222">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>6</v>
+      </c>
+      <c r="B223" t="s">
+        <v>229</v>
+      </c>
+      <c r="C223" t="s">
+        <v>504</v>
+      </c>
+      <c r="D223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>6</v>
+      </c>
+      <c r="B224" t="s">
+        <v>230</v>
+      </c>
+      <c r="C224" t="s">
+        <v>505</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>6</v>
+      </c>
+      <c r="B225" t="s">
+        <v>231</v>
+      </c>
+      <c r="C225" t="s">
+        <v>506</v>
+      </c>
+      <c r="D225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" t="s">
+        <v>232</v>
+      </c>
+      <c r="C226" t="s">
+        <v>507</v>
+      </c>
+      <c r="D226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>6</v>
+      </c>
+      <c r="B227" t="s">
+        <v>233</v>
+      </c>
+      <c r="C227" t="s">
+        <v>508</v>
+      </c>
+      <c r="D227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>6</v>
+      </c>
+      <c r="B228" t="s">
+        <v>234</v>
+      </c>
+      <c r="C228" t="s">
+        <v>509</v>
+      </c>
+      <c r="D228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>6</v>
+      </c>
+      <c r="B229" t="s">
+        <v>235</v>
+      </c>
+      <c r="C229" t="s">
+        <v>510</v>
+      </c>
+      <c r="D229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>6</v>
+      </c>
+      <c r="B230" t="s">
+        <v>236</v>
+      </c>
+      <c r="C230" t="s">
+        <v>511</v>
+      </c>
+      <c r="D230">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>6</v>
+      </c>
+      <c r="B231" t="s">
+        <v>237</v>
+      </c>
+      <c r="C231" t="s">
+        <v>512</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>6</v>
+      </c>
+      <c r="B232" t="s">
+        <v>238</v>
+      </c>
+      <c r="C232" t="s">
+        <v>513</v>
+      </c>
+      <c r="D232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>6</v>
+      </c>
+      <c r="B233" t="s">
+        <v>239</v>
+      </c>
+      <c r="C233" t="s">
+        <v>514</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" t="s">
+        <v>240</v>
+      </c>
+      <c r="C234" t="s">
+        <v>515</v>
+      </c>
+      <c r="D234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235" t="s">
+        <v>241</v>
+      </c>
+      <c r="C235" t="s">
+        <v>516</v>
+      </c>
+      <c r="D235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>6</v>
+      </c>
+      <c r="B236" t="s">
+        <v>242</v>
+      </c>
+      <c r="C236" t="s">
+        <v>517</v>
+      </c>
+      <c r="D236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>6</v>
+      </c>
+      <c r="B237" t="s">
+        <v>243</v>
+      </c>
+      <c r="C237" t="s">
+        <v>518</v>
+      </c>
+      <c r="D237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>6</v>
+      </c>
+      <c r="B238" t="s">
+        <v>244</v>
+      </c>
+      <c r="C238" t="s">
+        <v>519</v>
+      </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>6</v>
+      </c>
+      <c r="B239" t="s">
+        <v>245</v>
+      </c>
+      <c r="C239" t="s">
+        <v>520</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>6</v>
+      </c>
+      <c r="B240" t="s">
+        <v>246</v>
+      </c>
+      <c r="C240" t="s">
+        <v>521</v>
+      </c>
+      <c r="D240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>6</v>
+      </c>
+      <c r="B241" t="s">
+        <v>247</v>
+      </c>
+      <c r="C241" t="s">
+        <v>522</v>
+      </c>
+      <c r="D241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" t="s">
+        <v>248</v>
+      </c>
+      <c r="C242" t="s">
+        <v>523</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>6</v>
+      </c>
+      <c r="B243" t="s">
+        <v>249</v>
+      </c>
+      <c r="C243" t="s">
+        <v>524</v>
+      </c>
+      <c r="D243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>6</v>
+      </c>
+      <c r="B244" t="s">
+        <v>250</v>
+      </c>
+      <c r="C244" t="s">
+        <v>350</v>
+      </c>
+      <c r="D244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>6</v>
+      </c>
+      <c r="B245" t="s">
+        <v>251</v>
+      </c>
+      <c r="C245" t="s">
+        <v>525</v>
+      </c>
+      <c r="D245">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>7</v>
+      </c>
+      <c r="B246" t="s">
+        <v>252</v>
+      </c>
+      <c r="C246" t="s">
+        <v>526</v>
+      </c>
+      <c r="D246">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>7</v>
+      </c>
+      <c r="B247" t="s">
+        <v>253</v>
+      </c>
+      <c r="C247" t="s">
+        <v>527</v>
+      </c>
+      <c r="D247">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>7</v>
+      </c>
+      <c r="B248" t="s">
+        <v>254</v>
+      </c>
+      <c r="C248" t="s">
+        <v>528</v>
+      </c>
+      <c r="D248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>7</v>
+      </c>
+      <c r="B249" t="s">
+        <v>255</v>
+      </c>
+      <c r="C249" t="s">
+        <v>529</v>
+      </c>
+      <c r="D249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>7</v>
+      </c>
+      <c r="B250" t="s">
+        <v>256</v>
+      </c>
+      <c r="C250" t="s">
+        <v>530</v>
+      </c>
+      <c r="D250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>7</v>
+      </c>
+      <c r="B251" t="s">
+        <v>257</v>
+      </c>
+      <c r="C251" t="s">
+        <v>531</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>7</v>
+      </c>
+      <c r="B252" t="s">
+        <v>258</v>
+      </c>
+      <c r="C252" t="s">
+        <v>532</v>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>7</v>
+      </c>
+      <c r="B253" t="s">
+        <v>259</v>
+      </c>
+      <c r="C253" t="s">
+        <v>533</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>7</v>
+      </c>
+      <c r="B254" t="s">
+        <v>260</v>
+      </c>
+      <c r="C254" t="s">
+        <v>534</v>
+      </c>
+      <c r="D254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>7</v>
+      </c>
+      <c r="B255" t="s">
+        <v>261</v>
+      </c>
+      <c r="C255" t="s">
+        <v>535</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>7</v>
+      </c>
+      <c r="B256" t="s">
+        <v>262</v>
+      </c>
+      <c r="C256" t="s">
+        <v>536</v>
+      </c>
+      <c r="D256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>7</v>
+      </c>
+      <c r="B257" t="s">
+        <v>263</v>
+      </c>
+      <c r="C257" t="s">
+        <v>537</v>
+      </c>
+      <c r="D257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>7</v>
+      </c>
+      <c r="B258" t="s">
+        <v>264</v>
+      </c>
+      <c r="C258" t="s">
+        <v>538</v>
+      </c>
+      <c r="D258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
+        <v>7</v>
+      </c>
+      <c r="B259" t="s">
+        <v>265</v>
+      </c>
+      <c r="C259" t="s">
+        <v>539</v>
+      </c>
+      <c r="D259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>7</v>
+      </c>
+      <c r="B260" t="s">
+        <v>266</v>
+      </c>
+      <c r="C260" t="s">
+        <v>540</v>
+      </c>
+      <c r="D260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
+        <v>7</v>
+      </c>
+      <c r="B261" t="s">
+        <v>267</v>
+      </c>
+      <c r="C261" t="s">
+        <v>541</v>
+      </c>
+      <c r="D261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
+        <v>7</v>
+      </c>
+      <c r="B262" t="s">
+        <v>268</v>
+      </c>
+      <c r="C262" t="s">
+        <v>542</v>
+      </c>
+      <c r="D262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
+        <v>7</v>
+      </c>
+      <c r="B263" t="s">
+        <v>269</v>
+      </c>
+      <c r="C263" t="s">
+        <v>543</v>
+      </c>
+      <c r="D263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
+        <v>7</v>
+      </c>
+      <c r="B264" t="s">
+        <v>270</v>
+      </c>
+      <c r="C264" t="s">
+        <v>544</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>7</v>
+      </c>
+      <c r="B265" t="s">
+        <v>271</v>
+      </c>
+      <c r="C265" t="s">
+        <v>545</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
+        <v>7</v>
+      </c>
+      <c r="B266" t="s">
+        <v>272</v>
+      </c>
+      <c r="C266" t="s">
+        <v>546</v>
+      </c>
+      <c r="D266">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
+        <v>7</v>
+      </c>
+      <c r="B267" t="s">
+        <v>273</v>
+      </c>
+      <c r="C267" t="s">
+        <v>547</v>
+      </c>
+      <c r="D267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
+        <v>7</v>
+      </c>
+      <c r="B268" t="s">
+        <v>274</v>
+      </c>
+      <c r="C268" t="s">
+        <v>548</v>
+      </c>
+      <c r="D268">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
+        <v>7</v>
+      </c>
+      <c r="B269" t="s">
+        <v>275</v>
+      </c>
+      <c r="C269" t="s">
+        <v>549</v>
+      </c>
+      <c r="D269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
+        <v>7</v>
+      </c>
+      <c r="B270" t="s">
+        <v>276</v>
+      </c>
+      <c r="C270" t="s">
+        <v>550</v>
+      </c>
+      <c r="D270">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
+        <v>7</v>
+      </c>
+      <c r="B271" t="s">
+        <v>277</v>
+      </c>
+      <c r="C271" t="s">
+        <v>551</v>
+      </c>
+      <c r="D271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
+        <v>7</v>
+      </c>
+      <c r="B272" t="s">
+        <v>278</v>
+      </c>
+      <c r="C272" t="s">
+        <v>552</v>
+      </c>
+      <c r="D272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
+        <v>7</v>
+      </c>
+      <c r="B273" t="s">
+        <v>279</v>
+      </c>
+      <c r="C273" t="s">
+        <v>553</v>
+      </c>
+      <c r="D273">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
+        <v>7</v>
+      </c>
+      <c r="B274" t="s">
+        <v>280</v>
+      </c>
+      <c r="C274" t="s">
+        <v>554</v>
+      </c>
+      <c r="D274">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
+        <v>7</v>
+      </c>
+      <c r="B275" t="s">
+        <v>281</v>
+      </c>
+      <c r="C275" t="s">
+        <v>555</v>
+      </c>
+      <c r="D275">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
+        <v>7</v>
+      </c>
+      <c r="B276" t="s">
+        <v>282</v>
+      </c>
+      <c r="C276" t="s">
+        <v>556</v>
+      </c>
+      <c r="D276">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
